--- a/Data/Rules/Playology Rules Matrix.xlsx
+++ b/Data/Rules/Playology Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>4969393</t>
@@ -570,10 +573,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:AO18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -694,16 +697,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -816,16 +822,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>34</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -938,16 +947,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>34</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1060,16 +1072,19 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>34</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1182,16 +1197,19 @@
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>34</v>
+      </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1304,16 +1322,19 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>34</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1426,16 +1447,19 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>34</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1548,16 +1572,19 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>34</v>
+      </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1670,16 +1697,19 @@
       <c r="AN9">
         <v>0</v>
       </c>
+      <c r="AO9">
+        <v>34</v>
+      </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1792,16 +1822,19 @@
       <c r="AN10">
         <v>0</v>
       </c>
+      <c r="AO10">
+        <v>35</v>
+      </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:41">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1867,7 +1900,7 @@
         <v>2</v>
       </c>
       <c r="Y11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
@@ -1914,16 +1947,19 @@
       <c r="AN11">
         <v>0</v>
       </c>
+      <c r="AO11">
+        <v>36</v>
+      </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:41">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1989,7 +2025,7 @@
         <v>2</v>
       </c>
       <c r="Y12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
@@ -2036,16 +2072,19 @@
       <c r="AN12">
         <v>0</v>
       </c>
+      <c r="AO12">
+        <v>36</v>
+      </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:41">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2111,7 +2150,7 @@
         <v>2</v>
       </c>
       <c r="Y13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
@@ -2158,16 +2197,19 @@
       <c r="AN13">
         <v>0</v>
       </c>
+      <c r="AO13">
+        <v>36</v>
+      </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:41">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2233,7 +2275,7 @@
         <v>2</v>
       </c>
       <c r="Y14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
@@ -2280,16 +2322,19 @@
       <c r="AN14">
         <v>0</v>
       </c>
+      <c r="AO14">
+        <v>36</v>
+      </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:41">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2402,16 +2447,19 @@
       <c r="AN15">
         <v>0</v>
       </c>
+      <c r="AO15">
+        <v>34</v>
+      </c>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:41">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2524,16 +2572,19 @@
       <c r="AN16">
         <v>0</v>
       </c>
+      <c r="AO16">
+        <v>34</v>
+      </c>
     </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:41">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2646,16 +2697,19 @@
       <c r="AN17">
         <v>0</v>
       </c>
+      <c r="AO17">
+        <v>34</v>
+      </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:41">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2767,6 +2821,9 @@
       </c>
       <c r="AN18">
         <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
